--- a/threagile/output/tags.xlsx
+++ b/threagile/output/tags.xlsx
@@ -316,149 +316,127 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="23">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFF2600"/>
       <sz val="12"/>
-      <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF2600"/>
       <sz val="12"/>
-      <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFA0281E"/>
       <sz val="12"/>
-      <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFA0281E"/>
       <sz val="12"/>
-      <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFF8E00"/>
       <sz val="12"/>
-      <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF8E00"/>
       <sz val="12"/>
-      <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFC87832"/>
       <sz val="12"/>
-      <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFC87832"/>
       <sz val="12"/>
-      <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FF23465F"/>
       <sz val="12"/>
-      <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF23465F"/>
       <sz val="12"/>
-      <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF008F00"/>
       <sz val="12"/>
-      <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
       <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF40FF"/>
       <sz val="12"/>
-      <color rgb="FFFF40FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF9300"/>
       <sz val="12"/>
-      <color rgb="FFFF9300"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF666666"/>
       <sz val="12"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF7F7F7F"/>
       <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF008F00"/>
       <sz val="10"/>
-      <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
